--- a/ExcelDataAnalystic.xlsx
+++ b/ExcelDataAnalystic.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arafa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A35BEF29-570B-45C9-9849-78E171BEC8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFD9D1E-5454-4280-9CA9-C88745093593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="1020" windowWidth="12000" windowHeight="13815" xr2:uid="{97006FE0-67AF-4543-8924-70DF8F7F91D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{97006FE0-67AF-4543-8924-70DF8F7F91D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PivotTable" sheetId="4" r:id="rId1"/>
+    <sheet name="PivotTable (2)" sheetId="6" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="13" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,6 +41,170 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
+  <si>
+    <t>OrderID</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>OrderDate</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>johnsmith@gmail.com</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  new york</t>
+  </si>
+  <si>
+    <t>sarah_j@yahoo.com</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>dlee@hotmail.com</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>los angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> maria.g@gmail.com </t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>chrisb@gmail.com</t>
+  </si>
+  <si>
+    <t>USB Cable</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>emilyd@gmail.com</t>
+  </si>
+  <si>
+    <t>mwilson@gmail.com</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>alopez@gmail.com</t>
+  </si>
+  <si>
+    <t>houston</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>kadams@gmail.com</t>
+  </si>
+  <si>
+    <t>denver</t>
+  </si>
+  <si>
+    <t>maria.g@gmail.com</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>new york</t>
+  </si>
+  <si>
+    <t>Revenu</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Revenu</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>Sarah Johnson</t>
+  </si>
+  <si>
+    <t>David Lee</t>
+  </si>
+  <si>
+    <t>Maria Garcia</t>
+  </si>
+  <si>
+    <t>Chris Brown</t>
+  </si>
+  <si>
+    <t>Emily Davis</t>
+  </si>
+  <si>
+    <t>Michael Wilson</t>
+  </si>
+  <si>
+    <t>Anna Lopez</t>
+  </si>
+  <si>
+    <t>Kevin Adams</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>Count of Revenu</t>
+  </si>
+  <si>
+    <t>Count of Quantity</t>
+  </si>
+  <si>
+    <t>Sum of Revenu2</t>
+  </si>
+  <si>
+    <t>Count of Product</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +238,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -88,6 +268,3486 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ExcelDataAnalystic.xlsx]PivotTable!PivotTable3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Customers Total By Revenu</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTable!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of Revenu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTable!$A$4:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Emily Davis</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Michael Wilson</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Maria Garcia</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Chris Brown</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sarah Johnson</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>David Lee</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>John Smith</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Kevin Adams</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Anna Lopez</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTable!$B$4:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6761-42F2-8C6A-F89CADBEF0B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTable!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of Product</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTable!$A$4:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Emily Davis</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Michael Wilson</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Maria Garcia</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Chris Brown</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sarah Johnson</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>David Lee</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>John Smith</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Kevin Adams</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Anna Lopez</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTable!$C$4:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6761-42F2-8C6A-F89CADBEF0B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="170"/>
+        <c:overlap val="100"/>
+        <c:axId val="1482682527"/>
+        <c:axId val="1911564367"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1482682527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1911564367"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1911564367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1482682527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ExcelDataAnalystic.xlsx]PivotTable (2)!PivotTable3</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PivotTable (2)'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Revenu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'PivotTable (2)'!$A$4:$A$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>29.99</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>799</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>120</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>15.5</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5.99</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>(blank)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Keyboard</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Laptop</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Monitor</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Mouse</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>USB Cable</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>(blank)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PivotTable (2)'!$B$4:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>179.94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4794</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>139.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41.93</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9A48-4F77-96F3-424DDB037872}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PivotTable (2)'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of Quantity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'PivotTable (2)'!$A$4:$A$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>29.99</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>799</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>120</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>15.5</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5.99</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>(blank)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Keyboard</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Laptop</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Monitor</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Mouse</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>USB Cable</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>(blank)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PivotTable (2)'!$C$4:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9A48-4F77-96F3-424DDB037872}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PivotTable (2)'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Revenu2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'PivotTable (2)'!$A$4:$A$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>29.99</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>799</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>120</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>15.5</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5.99</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>(blank)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Keyboard</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Laptop</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Monitor</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Mouse</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>USB Cable</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>(blank)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PivotTable (2)'!$D$4:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3.0626156310155781E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.81594861259801499</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12254547373186708</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.3743185535549247E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.136571824412759E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9A48-4F77-96F3-424DDB037872}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="170"/>
+        <c:shape val="box"/>
+        <c:axId val="1482682527"/>
+        <c:axId val="1911564367"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1482682527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="00B0F0"/>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1911564367"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1911564367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1482682527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9716417-4F97-D398-59BA-5690B9C1312B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB1C8937-4087-46C8-B251-878235A703AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="arafat ouro gouni" refreshedDate="46314.955220833333" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="26" xr:uid="{AE06C33C-56A5-4A3C-958B-2735D91E9D95}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:I1048576" sheet="Dashboard"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="OrderID" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1025"/>
+    </cacheField>
+    <cacheField name="Customers" numFmtId="0">
+      <sharedItems containsBlank="1" count="10">
+        <s v="John Smith"/>
+        <s v="Sarah Johnson"/>
+        <s v="David Lee"/>
+        <s v="Maria Garcia"/>
+        <s v="Chris Brown"/>
+        <s v="Emily Davis"/>
+        <s v="Michael Wilson"/>
+        <s v="Anna Lopez"/>
+        <s v="Kevin Adams"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Email" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems containsBlank="1" count="6">
+        <s v="Keyboard"/>
+        <s v="Mouse"/>
+        <s v="Laptop"/>
+        <s v="Monitor"/>
+        <s v="USB Cable"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
+    </cacheField>
+    <cacheField name="Price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="5.99" maxValue="799" count="6">
+        <n v="29.99"/>
+        <n v="15.5"/>
+        <n v="799"/>
+        <n v="120"/>
+        <n v="5.99"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="OrderDate" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-01-03T00:00:00" maxDate="2024-01-13T00:00:00"/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Revenu" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="5.99" maxValue="799"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="26">
+  <r>
+    <n v="1001"/>
+    <x v="0"/>
+    <s v="johnsmith@gmail.com"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <d v="2024-01-03T00:00:00"/>
+    <s v="  new york"/>
+    <n v="29.99"/>
+  </r>
+  <r>
+    <n v="1002"/>
+    <x v="1"/>
+    <s v="sarah_j@yahoo.com"/>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="1"/>
+    <d v="2024-01-04T00:00:00"/>
+    <s v="Chicago"/>
+    <n v="31"/>
+  </r>
+  <r>
+    <n v="1003"/>
+    <x v="2"/>
+    <s v="dlee@hotmail.com"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <d v="2024-01-05T00:00:00"/>
+    <s v="los angeles"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <n v="1004"/>
+    <x v="3"/>
+    <s v=" maria.g@gmail.com "/>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="3"/>
+    <d v="2024-01-06T00:00:00"/>
+    <s v="Houston"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <n v="1005"/>
+    <x v="0"/>
+    <s v="johnsmith@gmail.com"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <d v="2024-01-03T00:00:00"/>
+    <s v="New York"/>
+    <n v="29.99"/>
+  </r>
+  <r>
+    <n v="1006"/>
+    <x v="4"/>
+    <s v="chrisb@gmail.com"/>
+    <x v="4"/>
+    <n v="3"/>
+    <x v="4"/>
+    <d v="2024-01-07T00:00:00"/>
+    <s v="Miami"/>
+    <n v="17.97"/>
+  </r>
+  <r>
+    <n v="1007"/>
+    <x v="5"/>
+    <s v="emilyd@gmail.com"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <d v="2024-01-08T00:00:00"/>
+    <s v="Chicago"/>
+    <n v="15.5"/>
+  </r>
+  <r>
+    <n v="1008"/>
+    <x v="6"/>
+    <s v="mwilson@gmail.com"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <d v="2024-01-09T00:00:00"/>
+    <s v="Seattle"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <n v="1009"/>
+    <x v="7"/>
+    <s v="alopez@gmail.com"/>
+    <x v="3"/>
+    <n v="2"/>
+    <x v="3"/>
+    <d v="2024-01-10T00:00:00"/>
+    <s v="Houston"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <n v="1010"/>
+    <x v="2"/>
+    <s v="dlee@hotmail.com"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <d v="2024-01-05T00:00:00"/>
+    <s v="los angeles"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <n v="1011"/>
+    <x v="8"/>
+    <s v="kadams@gmail.com"/>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <d v="2024-01-11T00:00:00"/>
+    <s v="denver"/>
+    <n v="59.98"/>
+  </r>
+  <r>
+    <n v="1012"/>
+    <x v="1"/>
+    <s v="sarah_j@yahoo.com"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <d v="2024-01-12T00:00:00"/>
+    <s v="Chicago"/>
+    <n v="15.5"/>
+  </r>
+  <r>
+    <n v="1013"/>
+    <x v="3"/>
+    <s v="maria.g@gmail.com"/>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="3"/>
+    <d v="2024-01-06T00:00:00"/>
+    <s v="Houston"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <n v="1014"/>
+    <x v="4"/>
+    <s v="chrisb@gmail.com"/>
+    <x v="4"/>
+    <n v="1"/>
+    <x v="4"/>
+    <d v="2024-01-07T00:00:00"/>
+    <s v="Miami"/>
+    <n v="5.99"/>
+  </r>
+  <r>
+    <n v="1015"/>
+    <x v="5"/>
+    <s v="emilyd@gmail.com"/>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="1"/>
+    <d v="2024-01-08T00:00:00"/>
+    <s v="Chicago"/>
+    <n v="31"/>
+  </r>
+  <r>
+    <n v="1016"/>
+    <x v="6"/>
+    <s v="mwilson@gmail.com"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <d v="2024-01-09T00:00:00"/>
+    <s v="Seattle"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <n v="1017"/>
+    <x v="7"/>
+    <s v="alopez@gmail.com"/>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="3"/>
+    <d v="2024-01-10T00:00:00"/>
+    <s v="Houston"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <n v="1018"/>
+    <x v="8"/>
+    <s v="kadams@gmail.com"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <d v="2024-01-11T00:00:00"/>
+    <s v="denver"/>
+    <n v="29.99"/>
+  </r>
+  <r>
+    <n v="1019"/>
+    <x v="0"/>
+    <s v="johnsmith@gmail.com"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <d v="2024-01-03T00:00:00"/>
+    <s v="New York"/>
+    <n v="29.99"/>
+  </r>
+  <r>
+    <n v="1020"/>
+    <x v="1"/>
+    <s v="sarah_j@yahoo.com"/>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="1"/>
+    <d v="2024-01-04T00:00:00"/>
+    <s v="Chicago"/>
+    <n v="31"/>
+  </r>
+  <r>
+    <n v="1021"/>
+    <x v="2"/>
+    <s v="dlee@hotmail.com"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <d v="2024-01-05T00:00:00"/>
+    <s v="los angeles"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <n v="1022"/>
+    <x v="3"/>
+    <s v=" maria.g@gmail.com "/>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="3"/>
+    <d v="2024-01-06T00:00:00"/>
+    <s v="Houston"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <n v="1023"/>
+    <x v="4"/>
+    <s v="chrisb@gmail.com"/>
+    <x v="4"/>
+    <n v="3"/>
+    <x v="4"/>
+    <d v="2024-01-07T00:00:00"/>
+    <s v="Miami"/>
+    <n v="17.97"/>
+  </r>
+  <r>
+    <n v="1024"/>
+    <x v="5"/>
+    <s v="emilyd@gmail.com"/>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <d v="2024-01-08T00:00:00"/>
+    <s v="Chicago"/>
+    <n v="15.5"/>
+  </r>
+  <r>
+    <n v="1025"/>
+    <x v="6"/>
+    <s v="mwilson@gmail.com"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <d v="2024-01-09T00:00:00"/>
+    <s v="Seattle"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <m/>
+    <x v="9"/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{35F1EAB2-791C-47C9-8A76-5BDFDCBAD578}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A3:C14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="11">
+        <item x="7"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Revenu" fld="8" subtotal="count" baseField="1" baseItem="0"/>
+    <dataField name="Count of Product" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CBBE914A-51E3-498A-ACB8-BCE2AE367DED}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:D16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" sortType="descending">
+      <items count="11">
+        <item x="7"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="3"/>
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Revenu" fld="8" baseField="1" baseItem="0" numFmtId="2"/>
+    <dataField name="Count of Quantity" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Revenu2" fld="8" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -406,10 +4066,1140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E75D664-1446-470C-9D8E-57CA0356D004}">
+  <dimension ref="A3:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="4">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465EBF03-95D1-4B09-86D5-E8CE1E25BBC3}">
+  <dimension ref="A3:D16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5">
+        <v>179.94</v>
+      </c>
+      <c r="C4" s="4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3.0626156310155781E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>29.99</v>
+      </c>
+      <c r="B5" s="5">
+        <v>179.94</v>
+      </c>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+      <c r="D5" s="7">
+        <v>3.0626156310155781E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5">
+        <v>4794</v>
+      </c>
+      <c r="C6" s="4">
+        <v>6</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.81594861259801499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>799</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4794</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.81594861259801499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5">
+        <v>720</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.12254547373186708</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>120</v>
+      </c>
+      <c r="B9" s="5">
+        <v>720</v>
+      </c>
+      <c r="C9" s="4">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.12254547373186708</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5">
+        <v>139.5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2.3743185535549247E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>15.5</v>
+      </c>
+      <c r="B11" s="5">
+        <v>139.5</v>
+      </c>
+      <c r="C11" s="4">
+        <v>6</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2.3743185535549247E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="5">
+        <v>41.93</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7">
+        <v>7.136571824412759E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>5.99</v>
+      </c>
+      <c r="B13" s="5">
+        <v>41.93</v>
+      </c>
+      <c r="C13" s="4">
+        <v>3</v>
+      </c>
+      <c r="D13" s="7">
+        <v>7.136571824412759E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5">
+        <v>5875.3700000000008</v>
+      </c>
+      <c r="C16" s="4">
+        <v>25</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D949ADA-3E77-42E8-AC68-1ABEC05F55BB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>29.99</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45294</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <f>E2 * F2</f>
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>15.5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45295</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I26" si="0">E3 * F3</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>799</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45296</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>120</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45297</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>29.99</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45294</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>5.99</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45298</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>17.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>15.5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45299</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>799</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45300</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>120</v>
+      </c>
+      <c r="G10" s="1">
+        <v>45301</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>799</v>
+      </c>
+      <c r="G11" s="1">
+        <v>45296</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>29.99</v>
+      </c>
+      <c r="G12" s="1">
+        <v>45302</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>59.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>15.5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>45303</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>120</v>
+      </c>
+      <c r="G14" s="1">
+        <v>45297</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>5.99</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45298</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>15.5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45299</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1016</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>799</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45300</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1017</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>120</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45301</v>
+      </c>
+      <c r="H18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1018</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>29.99</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45302</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1019</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>29.99</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45294</v>
+      </c>
+      <c r="H20" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>15.5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45295</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>799</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45296</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>120</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45297</v>
+      </c>
+      <c r="H23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>5.99</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45298</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>17.97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>15.5</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45299</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>799</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45300</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>